--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,339 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122747002</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79741</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rosenlund N, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>558934</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6902388</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På sälg i planerad hänsynsyta.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122747000</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90855</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Högbrännaberget S, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>558955</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6902417</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På högstubbe. Skulle varit med i kantzon.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122747001</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79741</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rosenlund N, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>558934</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6902381</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På sälg i kantzon</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Helene Andersson, Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>122747001</v>
       </c>
       <c r="B3" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>122747000</v>
       </c>
       <c r="B4" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>122747002</v>
       </c>
       <c r="B5" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747000</v>
+        <v>122747002</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,34 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Högbrännaberget S, Mpd</t>
+          <t>Rosenlund N, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558955</v>
+        <v>558934</v>
       </c>
       <c r="R4" t="n">
-        <v>6902417</v>
+        <v>6902388</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På högstubbe. Skulle varit med i kantzon.</t>
+          <t>På sälg i planerad hänsynsyta.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747002</v>
+        <v>122747000</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,34 +1029,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rosenlund N, Mpd</t>
+          <t>Högbrännaberget S, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558934</v>
+        <v>558955</v>
       </c>
       <c r="R5" t="n">
-        <v>6902388</v>
+        <v>6902417</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälg i planerad hänsynsyta.</t>
+          <t>På högstubbe. Skulle varit med i kantzon.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747002</v>
+        <v>122747000</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,34 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rosenlund N, Mpd</t>
+          <t>Högbrännaberget S, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558934</v>
+        <v>558955</v>
       </c>
       <c r="R4" t="n">
-        <v>6902388</v>
+        <v>6902417</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På sälg i planerad hänsynsyta.</t>
+          <t>På högstubbe. Skulle varit med i kantzon.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747000</v>
+        <v>122747002</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,34 +1029,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Högbrännaberget S, Mpd</t>
+          <t>Rosenlund N, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558955</v>
+        <v>558934</v>
       </c>
       <c r="R5" t="n">
-        <v>6902417</v>
+        <v>6902388</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På högstubbe. Skulle varit med i kantzon.</t>
+          <t>På sälg i planerad hänsynsyta.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747000</v>
+        <v>122747002</v>
       </c>
       <c r="B4" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,34 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Högbrännaberget S, Mpd</t>
+          <t>Rosenlund N, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558955</v>
+        <v>558934</v>
       </c>
       <c r="R4" t="n">
-        <v>6902417</v>
+        <v>6902388</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På högstubbe. Skulle varit med i kantzon.</t>
+          <t>På sälg i planerad hänsynsyta.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747002</v>
+        <v>122747000</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,34 +1029,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rosenlund N, Mpd</t>
+          <t>Högbrännaberget S, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558934</v>
+        <v>558955</v>
       </c>
       <c r="R5" t="n">
-        <v>6902388</v>
+        <v>6902417</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälg i planerad hänsynsyta.</t>
+          <t>På högstubbe. Skulle varit med i kantzon.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747001</v>
+        <v>122747000</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rosenlund N, Mpd</t>
+          <t>Högbrännaberget S, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558934</v>
+        <v>558955</v>
       </c>
       <c r="R3" t="n">
-        <v>6902381</v>
+        <v>6902417</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På sälg i kantzon</t>
+          <t>På högstubbe. Skulle varit med i kantzon.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747000</v>
+        <v>122747001</v>
       </c>
       <c r="B5" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,34 +1029,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Högbrännaberget S, Mpd</t>
+          <t>Rosenlund N, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558955</v>
+        <v>558934</v>
       </c>
       <c r="R5" t="n">
-        <v>6902417</v>
+        <v>6902381</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På högstubbe. Skulle varit med i kantzon.</t>
+          <t>På sälg i kantzon</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747000</v>
+        <v>122747001</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högbrännaberget S, Mpd</t>
+          <t>Rosenlund N, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558955</v>
+        <v>558934</v>
       </c>
       <c r="R3" t="n">
-        <v>6902417</v>
+        <v>6902381</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På högstubbe. Skulle varit med i kantzon.</t>
+          <t>På sälg i kantzon</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747001</v>
+        <v>122747000</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,34 +1029,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rosenlund N, Mpd</t>
+          <t>Högbrännaberget S, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558934</v>
+        <v>558955</v>
       </c>
       <c r="R5" t="n">
-        <v>6902381</v>
+        <v>6902417</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälg i kantzon</t>
+          <t>På högstubbe. Skulle varit med i kantzon.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>122747001</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122747002</v>
+        <v>122747000</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>90973</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,34 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rosenlund N, Mpd</t>
+          <t>Högbrännaberget S, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558934</v>
+        <v>558955</v>
       </c>
       <c r="R4" t="n">
-        <v>6902388</v>
+        <v>6902417</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På sälg i planerad hänsynsyta.</t>
+          <t>På högstubbe. Skulle varit med i kantzon.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747000</v>
+        <v>122747002</v>
       </c>
       <c r="B5" t="n">
-        <v>90970</v>
+        <v>79850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,34 +1029,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Högbrännaberget S, Mpd</t>
+          <t>Rosenlund N, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>558955</v>
+        <v>558934</v>
       </c>
       <c r="R5" t="n">
-        <v>6902417</v>
+        <v>6902388</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På högstubbe. Skulle varit med i kantzon.</t>
+          <t>På sälg i planerad hänsynsyta.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122747001</v>
+        <v>122747002</v>
       </c>
       <c r="B3" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         <v>558934</v>
       </c>
       <c r="R3" t="n">
-        <v>6902381</v>
+        <v>6902388</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På sälg i kantzon</t>
+          <t>På sälg i planerad hänsynsyta.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +905,7 @@
         <v>122747000</v>
       </c>
       <c r="B4" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122747002</v>
+        <v>122747001</v>
       </c>
       <c r="B5" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>558934</v>
       </c>
       <c r="R5" t="n">
-        <v>6902388</v>
+        <v>6902381</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På sälg i planerad hänsynsyta.</t>
+          <t>På sälg i kantzon</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1122,6 +1122,2777 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131738280</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80365</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Pållesmyran Sydost, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>558915</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6902471</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131738275</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80365</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Pållesmyran Syd, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>558928</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6902570</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131736631</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80366</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Pållesmyran Syd, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>558932</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6902496</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131740502</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80394</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Pållesmyran Syd, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>558929</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6902492</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131735295</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99034</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Pållesmyran Sydost, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>558934</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6902394</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor ligger i hänsyn</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131734446</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99371</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Pållesmyran Sydost, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>558914</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6902441</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131731706</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Pållesmyran Sydväst, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>558898</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6902580</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla granar i myrkant</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131735296</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99034</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Pållesmyran Sydost, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>558940</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6902312</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131734447</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99371</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Pållesmyran Sydost, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>558943</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6902405</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131736743</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80269</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Pållesmyran Sydväst, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>558929</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6902582</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131735294</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99034</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Pållesmyran Sydost, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>558938</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6902400</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131731709</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Pållesmyran Sydost, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>558907</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6902446</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131739130</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79879</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Pållesmyran Öst, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>558859</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6902252</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På mycket fin talltorraka</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131737207</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97905</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Pållesmyran Öst, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>558887</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6902256</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131733537</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79516</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Pållesmyran Syd, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>558903</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6902511</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På torrgran med doftskinn</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131731707</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Pållesmyran Syd, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>558907</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6902516</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt på björk i hänsyn</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131738278</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80365</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Pållesmyran Sydväst, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>558913</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6902578</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131734449</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99371</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Pållesmyran Sydost, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>558937</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6902393</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131737206</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97905</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Pållesmyran Sydost, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>558937</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6902314</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>I hänsyn med knärot</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131731708</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Pållesmyran Syd, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>558898</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6902495</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gamla granar mot våtmark</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131738281</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80365</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Pållesmyran Sydost, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>558951</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6902326</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På sälg i hänsyn</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131736629</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80366</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Pållesmyran Syd, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>558916</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6902571</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131738277</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80365</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Pållesmyran Syd, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>558914</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6902572</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131738279</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80365</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Pållesmyran Syd, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>558933</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6902494</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131732429</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98951</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Pållesmyran Öst, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>558902</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6902247</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131732929</v>
+      </c>
+      <c r="B31" t="n">
+        <v>89213</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>510</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Pållesmyran Syd, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>558900</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6902511</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131740501</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80394</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Pållesmyran Sydväst, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>558908</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6902578</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -2350,32 +2350,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131739130</v>
+        <v>131737207</v>
       </c>
       <c r="B18" t="n">
-        <v>79879</v>
+        <v>97905</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558859</v>
+        <v>558887</v>
       </c>
       <c r="R18" t="n">
-        <v>6902252</v>
+        <v>6902256</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2421,11 +2421,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På mycket fin talltorraka</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2456,32 +2451,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737207</v>
+        <v>131739130</v>
       </c>
       <c r="B19" t="n">
-        <v>97905</v>
+        <v>79879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2491,10 +2486,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558887</v>
+        <v>558859</v>
       </c>
       <c r="R19" t="n">
-        <v>6902256</v>
+        <v>6902252</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2527,6 +2522,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På mycket fin talltorraka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2769,45 +2769,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131738278</v>
+        <v>131737206</v>
       </c>
       <c r="B22" t="n">
-        <v>80365</v>
+        <v>97905</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydväst, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558913</v>
+        <v>558937</v>
       </c>
       <c r="R22" t="n">
-        <v>6902578</v>
+        <v>6902314</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2840,6 +2840,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>I hänsyn med knärot</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2870,45 +2875,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131734449</v>
+        <v>131738278</v>
       </c>
       <c r="B23" t="n">
-        <v>99371</v>
+        <v>80365</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558937</v>
+        <v>558913</v>
       </c>
       <c r="R23" t="n">
-        <v>6902393</v>
+        <v>6902578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2971,10 +2976,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131737206</v>
+        <v>131734449</v>
       </c>
       <c r="B24" t="n">
-        <v>97905</v>
+        <v>99371</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2982,21 +2987,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>219880</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3009,7 +3014,7 @@
         <v>558937</v>
       </c>
       <c r="R24" t="n">
-        <v>6902314</v>
+        <v>6902393</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3042,11 +3047,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>I hänsyn med knärot</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3491,45 +3491,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131738279</v>
+        <v>131732429</v>
       </c>
       <c r="B29" t="n">
-        <v>80365</v>
+        <v>98951</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pållesmyran Syd, Mpd</t>
+          <t>Pållesmyran Öst, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558933</v>
+        <v>558902</v>
       </c>
       <c r="R29" t="n">
-        <v>6902494</v>
+        <v>6902247</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3592,45 +3592,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131732429</v>
+        <v>131732929</v>
       </c>
       <c r="B30" t="n">
-        <v>98951</v>
+        <v>89213</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pållesmyran Öst, Mpd</t>
+          <t>Pållesmyran Syd, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558902</v>
+        <v>558900</v>
       </c>
       <c r="R30" t="n">
-        <v>6902247</v>
+        <v>6902511</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131732929</v>
+        <v>131738279</v>
       </c>
       <c r="B31" t="n">
-        <v>89213</v>
+        <v>80365</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3704,21 +3704,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558900</v>
+        <v>558933</v>
       </c>
       <c r="R31" t="n">
-        <v>6902511</v>
+        <v>6902494</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -1127,7 +1127,7 @@
         <v>131738280</v>
       </c>
       <c r="B6" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>131738275</v>
       </c>
       <c r="B7" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>131736631</v>
       </c>
       <c r="B8" t="n">
-        <v>80366</v>
+        <v>80367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>131740502</v>
       </c>
       <c r="B9" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>131735295</v>
       </c>
       <c r="B10" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>131734446</v>
       </c>
       <c r="B11" t="n">
-        <v>99371</v>
+        <v>99372</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>131731706</v>
       </c>
       <c r="B12" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>131735296</v>
       </c>
       <c r="B13" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131734447</v>
+        <v>131736743</v>
       </c>
       <c r="B14" t="n">
-        <v>99371</v>
+        <v>80270</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1957,34 +1957,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219880</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558943</v>
+        <v>558929</v>
       </c>
       <c r="R14" t="n">
-        <v>6902405</v>
+        <v>6902582</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131736743</v>
+        <v>131734447</v>
       </c>
       <c r="B15" t="n">
-        <v>80269</v>
+        <v>99372</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2058,34 +2058,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>219880</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydväst, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558929</v>
+        <v>558943</v>
       </c>
       <c r="R15" t="n">
-        <v>6902582</v>
+        <v>6902405</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,32 +2148,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131735294</v>
+        <v>131731709</v>
       </c>
       <c r="B16" t="n">
-        <v>99034</v>
+        <v>79261</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558938</v>
+        <v>558907</v>
       </c>
       <c r="R16" t="n">
-        <v>6902400</v>
+        <v>6902446</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,32 +2249,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131731709</v>
+        <v>131735294</v>
       </c>
       <c r="B17" t="n">
-        <v>79260</v>
+        <v>99035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558907</v>
+        <v>558938</v>
       </c>
       <c r="R17" t="n">
-        <v>6902446</v>
+        <v>6902400</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,32 +2350,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131737207</v>
+        <v>131739130</v>
       </c>
       <c r="B18" t="n">
-        <v>97905</v>
+        <v>79880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558887</v>
+        <v>558859</v>
       </c>
       <c r="R18" t="n">
-        <v>6902256</v>
+        <v>6902252</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2421,6 +2421,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På mycket fin talltorraka</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2451,32 +2456,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131739130</v>
+        <v>131737207</v>
       </c>
       <c r="B19" t="n">
-        <v>79879</v>
+        <v>97906</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2486,10 +2491,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558859</v>
+        <v>558887</v>
       </c>
       <c r="R19" t="n">
-        <v>6902252</v>
+        <v>6902256</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2522,11 +2527,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På mycket fin talltorraka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2560,7 +2560,7 @@
         <v>131733537</v>
       </c>
       <c r="B20" t="n">
-        <v>79516</v>
+        <v>79517</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>131731707</v>
       </c>
       <c r="B21" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2769,45 +2769,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737206</v>
+        <v>131738278</v>
       </c>
       <c r="B22" t="n">
-        <v>97905</v>
+        <v>80366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558937</v>
+        <v>558913</v>
       </c>
       <c r="R22" t="n">
-        <v>6902314</v>
+        <v>6902578</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2840,11 +2840,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>I hänsyn med knärot</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2875,10 +2870,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131738278</v>
+        <v>131731708</v>
       </c>
       <c r="B23" t="n">
-        <v>80365</v>
+        <v>79261</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2886,34 +2881,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydväst, Mpd</t>
+          <t>Pållesmyran Syd, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558913</v>
+        <v>558898</v>
       </c>
       <c r="R23" t="n">
-        <v>6902578</v>
+        <v>6902495</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2946,6 +2941,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gamla granar mot våtmark</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2979,7 +2979,7 @@
         <v>131734449</v>
       </c>
       <c r="B24" t="n">
-        <v>99371</v>
+        <v>99372</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3077,45 +3077,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131731708</v>
+        <v>131737206</v>
       </c>
       <c r="B25" t="n">
-        <v>79260</v>
+        <v>97906</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pållesmyran Syd, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558898</v>
+        <v>558937</v>
       </c>
       <c r="R25" t="n">
-        <v>6902495</v>
+        <v>6902314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gamla granar mot våtmark</t>
+          <t>I hänsyn med knärot</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3186,7 +3186,7 @@
         <v>131738281</v>
       </c>
       <c r="B26" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>131736629</v>
       </c>
       <c r="B27" t="n">
-        <v>80366</v>
+        <v>80367</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>131738277</v>
       </c>
       <c r="B28" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,45 +3491,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131732429</v>
+        <v>131732929</v>
       </c>
       <c r="B29" t="n">
-        <v>98951</v>
+        <v>89214</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pållesmyran Öst, Mpd</t>
+          <t>Pållesmyran Syd, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558902</v>
+        <v>558900</v>
       </c>
       <c r="R29" t="n">
-        <v>6902247</v>
+        <v>6902511</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3592,10 +3592,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131732929</v>
+        <v>131738279</v>
       </c>
       <c r="B30" t="n">
-        <v>89213</v>
+        <v>80366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558900</v>
+        <v>558933</v>
       </c>
       <c r="R30" t="n">
-        <v>6902511</v>
+        <v>6902494</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3693,45 +3693,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131738279</v>
+        <v>131732429</v>
       </c>
       <c r="B31" t="n">
-        <v>80365</v>
+        <v>98952</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pållesmyran Syd, Mpd</t>
+          <t>Pållesmyran Öst, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558933</v>
+        <v>558902</v>
       </c>
       <c r="R31" t="n">
-        <v>6902494</v>
+        <v>6902247</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3797,7 +3797,7 @@
         <v>131740501</v>
       </c>
       <c r="B32" t="n">
-        <v>80394</v>
+        <v>80395</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -1127,7 +1127,7 @@
         <v>131738280</v>
       </c>
       <c r="B6" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>131738275</v>
       </c>
       <c r="B7" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>131736631</v>
       </c>
       <c r="B8" t="n">
-        <v>80367</v>
+        <v>80370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>131740502</v>
       </c>
       <c r="B9" t="n">
-        <v>80395</v>
+        <v>80398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>131735295</v>
       </c>
       <c r="B10" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>131734446</v>
       </c>
       <c r="B11" t="n">
-        <v>99372</v>
+        <v>99375</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1739,45 +1739,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131731706</v>
+        <v>131735296</v>
       </c>
       <c r="B12" t="n">
-        <v>79261</v>
+        <v>99038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydväst, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558898</v>
+        <v>558940</v>
       </c>
       <c r="R12" t="n">
-        <v>6902580</v>
+        <v>6902312</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,11 +1810,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt på gamla granar i myrkant</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,45 +1840,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131735296</v>
+        <v>131731706</v>
       </c>
       <c r="B13" t="n">
-        <v>99035</v>
+        <v>79264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558940</v>
+        <v>558898</v>
       </c>
       <c r="R13" t="n">
-        <v>6902312</v>
+        <v>6902580</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,6 +1911,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla granar i myrkant</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1949,7 @@
         <v>131736743</v>
       </c>
       <c r="B14" t="n">
-        <v>80270</v>
+        <v>80273</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>131734447</v>
       </c>
       <c r="B15" t="n">
-        <v>99372</v>
+        <v>99375</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,32 +2148,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131731709</v>
+        <v>131735294</v>
       </c>
       <c r="B16" t="n">
-        <v>79261</v>
+        <v>99038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558907</v>
+        <v>558938</v>
       </c>
       <c r="R16" t="n">
-        <v>6902446</v>
+        <v>6902400</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,32 +2249,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131735294</v>
+        <v>131731709</v>
       </c>
       <c r="B17" t="n">
-        <v>99035</v>
+        <v>79264</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558938</v>
+        <v>558907</v>
       </c>
       <c r="R17" t="n">
-        <v>6902400</v>
+        <v>6902446</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,7 +2353,7 @@
         <v>131739130</v>
       </c>
       <c r="B18" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>131737207</v>
       </c>
       <c r="B19" t="n">
-        <v>97906</v>
+        <v>97909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2557,32 +2557,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131733537</v>
+        <v>131731707</v>
       </c>
       <c r="B20" t="n">
-        <v>79517</v>
+        <v>79264</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558903</v>
+        <v>558907</v>
       </c>
       <c r="R20" t="n">
-        <v>6902511</v>
+        <v>6902516</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På torrgran med doftskinn</t>
+          <t>Rikligt på björk i hänsyn</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,32 +2663,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131731707</v>
+        <v>131733537</v>
       </c>
       <c r="B21" t="n">
-        <v>79261</v>
+        <v>79520</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558907</v>
+        <v>558903</v>
       </c>
       <c r="R21" t="n">
-        <v>6902516</v>
+        <v>6902511</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt på björk i hänsyn</t>
+          <t>På torrgran med doftskinn</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2769,10 +2769,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131738278</v>
+        <v>131731708</v>
       </c>
       <c r="B22" t="n">
-        <v>80366</v>
+        <v>79264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,34 +2780,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydväst, Mpd</t>
+          <t>Pållesmyran Syd, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558913</v>
+        <v>558898</v>
       </c>
       <c r="R22" t="n">
-        <v>6902578</v>
+        <v>6902495</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2840,6 +2840,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gamla granar mot våtmark</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2870,10 +2875,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131731708</v>
+        <v>131738278</v>
       </c>
       <c r="B23" t="n">
-        <v>79261</v>
+        <v>80369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2881,34 +2886,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pållesmyran Syd, Mpd</t>
+          <t>Pållesmyran Sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558898</v>
+        <v>558913</v>
       </c>
       <c r="R23" t="n">
-        <v>6902495</v>
+        <v>6902578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2941,11 +2946,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gamla granar mot våtmark</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2976,10 +2976,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131734449</v>
+        <v>131737206</v>
       </c>
       <c r="B24" t="n">
-        <v>99372</v>
+        <v>97909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2987,21 +2987,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219880</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3014,7 +3014,7 @@
         <v>558937</v>
       </c>
       <c r="R24" t="n">
-        <v>6902393</v>
+        <v>6902314</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3047,6 +3047,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>I hänsyn med knärot</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3077,10 +3082,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131737206</v>
+        <v>131734449</v>
       </c>
       <c r="B25" t="n">
-        <v>97906</v>
+        <v>99375</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3088,21 +3093,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>219880</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3115,7 +3120,7 @@
         <v>558937</v>
       </c>
       <c r="R25" t="n">
-        <v>6902314</v>
+        <v>6902393</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3148,11 +3153,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>I hänsyn med knärot</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131738281</v>
+        <v>131736629</v>
       </c>
       <c r="B26" t="n">
-        <v>80366</v>
+        <v>80370</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,34 +3194,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Syd, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558951</v>
+        <v>558916</v>
       </c>
       <c r="R26" t="n">
-        <v>6902326</v>
+        <v>6902571</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3254,11 +3254,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På sälg i hänsyn</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3289,10 +3284,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131736629</v>
+        <v>131738281</v>
       </c>
       <c r="B27" t="n">
-        <v>80367</v>
+        <v>80369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3300,34 +3295,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pållesmyran Syd, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558916</v>
+        <v>558951</v>
       </c>
       <c r="R27" t="n">
-        <v>6902571</v>
+        <v>6902326</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3360,6 +3355,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På sälg i hänsyn</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3393,7 +3393,7 @@
         <v>131738277</v>
       </c>
       <c r="B28" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,10 +3491,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131732929</v>
+        <v>131738279</v>
       </c>
       <c r="B29" t="n">
-        <v>89214</v>
+        <v>80369</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3502,21 +3502,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558900</v>
+        <v>558933</v>
       </c>
       <c r="R29" t="n">
-        <v>6902511</v>
+        <v>6902494</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3592,45 +3592,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131738279</v>
+        <v>131732429</v>
       </c>
       <c r="B30" t="n">
-        <v>80366</v>
+        <v>98955</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pållesmyran Syd, Mpd</t>
+          <t>Pållesmyran Öst, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558933</v>
+        <v>558902</v>
       </c>
       <c r="R30" t="n">
-        <v>6902494</v>
+        <v>6902247</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3693,45 +3693,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131732429</v>
+        <v>131732929</v>
       </c>
       <c r="B31" t="n">
-        <v>98952</v>
+        <v>89217</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pållesmyran Öst, Mpd</t>
+          <t>Pållesmyran Syd, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558902</v>
+        <v>558900</v>
       </c>
       <c r="R31" t="n">
-        <v>6902247</v>
+        <v>6902511</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3797,7 +3797,7 @@
         <v>131740501</v>
       </c>
       <c r="B32" t="n">
-        <v>80395</v>
+        <v>80398</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -1739,45 +1739,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131735296</v>
+        <v>131731706</v>
       </c>
       <c r="B12" t="n">
-        <v>99038</v>
+        <v>79264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558940</v>
+        <v>558898</v>
       </c>
       <c r="R12" t="n">
-        <v>6902312</v>
+        <v>6902580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,6 +1810,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla granar i myrkant</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1840,45 +1845,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131731706</v>
+        <v>131735296</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>99038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydväst, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558898</v>
+        <v>558940</v>
       </c>
       <c r="R13" t="n">
-        <v>6902580</v>
+        <v>6902312</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,11 +1916,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt på gamla granar i myrkant</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2557,32 +2557,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131731707</v>
+        <v>131733537</v>
       </c>
       <c r="B20" t="n">
-        <v>79264</v>
+        <v>79520</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558907</v>
+        <v>558903</v>
       </c>
       <c r="R20" t="n">
-        <v>6902516</v>
+        <v>6902511</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt på björk i hänsyn</t>
+          <t>På torrgran med doftskinn</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,32 +2663,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131733537</v>
+        <v>131731707</v>
       </c>
       <c r="B21" t="n">
-        <v>79520</v>
+        <v>79264</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558903</v>
+        <v>558907</v>
       </c>
       <c r="R21" t="n">
-        <v>6902511</v>
+        <v>6902516</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På torrgran med doftskinn</t>
+          <t>Rikligt på björk i hänsyn</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2875,45 +2875,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131738278</v>
+        <v>131734449</v>
       </c>
       <c r="B23" t="n">
-        <v>80369</v>
+        <v>99375</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydväst, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558913</v>
+        <v>558937</v>
       </c>
       <c r="R23" t="n">
-        <v>6902578</v>
+        <v>6902393</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3082,45 +3082,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131734449</v>
+        <v>131738278</v>
       </c>
       <c r="B25" t="n">
-        <v>99375</v>
+        <v>80369</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558937</v>
+        <v>558913</v>
       </c>
       <c r="R25" t="n">
-        <v>6902393</v>
+        <v>6902578</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3183,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131736629</v>
+        <v>131738281</v>
       </c>
       <c r="B26" t="n">
-        <v>80370</v>
+        <v>80369</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,34 +3194,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pållesmyran Syd, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558916</v>
+        <v>558951</v>
       </c>
       <c r="R26" t="n">
-        <v>6902571</v>
+        <v>6902326</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3254,6 +3254,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På sälg i hänsyn</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3284,10 +3289,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131738281</v>
+        <v>131736629</v>
       </c>
       <c r="B27" t="n">
-        <v>80369</v>
+        <v>80370</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3295,34 +3300,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Syd, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558951</v>
+        <v>558916</v>
       </c>
       <c r="R27" t="n">
-        <v>6902326</v>
+        <v>6902571</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3355,11 +3360,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På sälg i hänsyn</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3491,10 +3491,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131738279</v>
+        <v>131732929</v>
       </c>
       <c r="B29" t="n">
-        <v>80369</v>
+        <v>89217</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3502,21 +3502,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558933</v>
+        <v>558900</v>
       </c>
       <c r="R29" t="n">
-        <v>6902494</v>
+        <v>6902511</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3693,10 +3693,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131732929</v>
+        <v>131738279</v>
       </c>
       <c r="B31" t="n">
-        <v>89217</v>
+        <v>80369</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3704,21 +3704,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558900</v>
+        <v>558933</v>
       </c>
       <c r="R31" t="n">
-        <v>6902511</v>
+        <v>6902494</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -1739,45 +1739,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131731706</v>
+        <v>131735296</v>
       </c>
       <c r="B12" t="n">
-        <v>79264</v>
+        <v>99038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydväst, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558898</v>
+        <v>558940</v>
       </c>
       <c r="R12" t="n">
-        <v>6902580</v>
+        <v>6902312</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,11 +1810,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt på gamla granar i myrkant</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,45 +1840,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131735296</v>
+        <v>131731706</v>
       </c>
       <c r="B13" t="n">
-        <v>99038</v>
+        <v>79264</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558940</v>
+        <v>558898</v>
       </c>
       <c r="R13" t="n">
-        <v>6902312</v>
+        <v>6902580</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1916,6 +1911,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla granar i myrkant</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2769,10 +2769,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131731708</v>
+        <v>131738278</v>
       </c>
       <c r="B22" t="n">
-        <v>79264</v>
+        <v>80369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,34 +2780,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pållesmyran Syd, Mpd</t>
+          <t>Pållesmyran Sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558898</v>
+        <v>558913</v>
       </c>
       <c r="R22" t="n">
-        <v>6902495</v>
+        <v>6902578</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2840,11 +2840,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På gamla granar mot våtmark</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2875,45 +2870,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131734449</v>
+        <v>131731708</v>
       </c>
       <c r="B23" t="n">
-        <v>99375</v>
+        <v>79264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Syd, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558937</v>
+        <v>558898</v>
       </c>
       <c r="R23" t="n">
-        <v>6902393</v>
+        <v>6902495</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2946,6 +2941,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gamla granar mot våtmark</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2976,10 +2976,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131737206</v>
+        <v>131734449</v>
       </c>
       <c r="B24" t="n">
-        <v>97909</v>
+        <v>99375</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2987,21 +2987,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>219880</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3014,7 +3014,7 @@
         <v>558937</v>
       </c>
       <c r="R24" t="n">
-        <v>6902314</v>
+        <v>6902393</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3047,11 +3047,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>I hänsyn med knärot</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3082,45 +3077,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131738278</v>
+        <v>131737206</v>
       </c>
       <c r="B25" t="n">
-        <v>80369</v>
+        <v>97909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydväst, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558913</v>
+        <v>558937</v>
       </c>
       <c r="R25" t="n">
-        <v>6902578</v>
+        <v>6902314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3153,6 +3148,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I hänsyn med knärot</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3183,10 +3183,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131738281</v>
+        <v>131736629</v>
       </c>
       <c r="B26" t="n">
-        <v>80369</v>
+        <v>80370</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3194,34 +3194,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Syd, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>558951</v>
+        <v>558916</v>
       </c>
       <c r="R26" t="n">
-        <v>6902326</v>
+        <v>6902571</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3254,11 +3254,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På sälg i hänsyn</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3289,10 +3284,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131736629</v>
+        <v>131738281</v>
       </c>
       <c r="B27" t="n">
-        <v>80370</v>
+        <v>80369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3300,34 +3295,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Pållesmyran Syd, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>558916</v>
+        <v>558951</v>
       </c>
       <c r="R27" t="n">
-        <v>6902571</v>
+        <v>6902326</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3360,6 +3355,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På sälg i hänsyn</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3491,45 +3491,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131732929</v>
+        <v>131732429</v>
       </c>
       <c r="B29" t="n">
-        <v>89217</v>
+        <v>98955</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pållesmyran Syd, Mpd</t>
+          <t>Pållesmyran Öst, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558900</v>
+        <v>558902</v>
       </c>
       <c r="R29" t="n">
-        <v>6902511</v>
+        <v>6902247</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3592,45 +3592,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131732429</v>
+        <v>131732929</v>
       </c>
       <c r="B30" t="n">
-        <v>98955</v>
+        <v>89217</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219790</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Pållesmyran Öst, Mpd</t>
+          <t>Pållesmyran Syd, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558902</v>
+        <v>558900</v>
       </c>
       <c r="R30" t="n">
-        <v>6902247</v>
+        <v>6902511</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -1739,45 +1739,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131735296</v>
+        <v>131731706</v>
       </c>
       <c r="B12" t="n">
-        <v>99038</v>
+        <v>79264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>558940</v>
+        <v>558898</v>
       </c>
       <c r="R12" t="n">
-        <v>6902312</v>
+        <v>6902580</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,6 +1810,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla granar i myrkant</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1840,45 +1845,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131731706</v>
+        <v>131735296</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>99038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydväst, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>558898</v>
+        <v>558940</v>
       </c>
       <c r="R13" t="n">
-        <v>6902580</v>
+        <v>6902312</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1911,11 +1916,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt på gamla granar i myrkant</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2769,45 +2769,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131738278</v>
+        <v>131734449</v>
       </c>
       <c r="B22" t="n">
-        <v>80369</v>
+        <v>99375</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>219880</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydväst, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>558913</v>
+        <v>558937</v>
       </c>
       <c r="R22" t="n">
-        <v>6902578</v>
+        <v>6902393</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2870,45 +2870,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131731708</v>
+        <v>131737206</v>
       </c>
       <c r="B23" t="n">
-        <v>79264</v>
+        <v>97909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pållesmyran Syd, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558898</v>
+        <v>558937</v>
       </c>
       <c r="R23" t="n">
-        <v>6902495</v>
+        <v>6902314</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gamla granar mot våtmark</t>
+          <t>I hänsyn med knärot</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2976,45 +2976,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131734449</v>
+        <v>131738278</v>
       </c>
       <c r="B24" t="n">
-        <v>99375</v>
+        <v>80369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558937</v>
+        <v>558913</v>
       </c>
       <c r="R24" t="n">
-        <v>6902393</v>
+        <v>6902578</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3077,45 +3077,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131737206</v>
+        <v>131731708</v>
       </c>
       <c r="B25" t="n">
-        <v>97909</v>
+        <v>79264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Syd, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558937</v>
+        <v>558898</v>
       </c>
       <c r="R25" t="n">
-        <v>6902314</v>
+        <v>6902495</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I hänsyn med knärot</t>
+          <t>På gamla granar mot våtmark</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -1127,7 +1127,7 @@
         <v>131738280</v>
       </c>
       <c r="B6" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>131738275</v>
       </c>
       <c r="B7" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
         <v>131736631</v>
       </c>
       <c r="B8" t="n">
-        <v>80370</v>
+        <v>80372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>131740502</v>
       </c>
       <c r="B9" t="n">
-        <v>80398</v>
+        <v>80400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>131735295</v>
       </c>
       <c r="B10" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>131734446</v>
       </c>
       <c r="B11" t="n">
-        <v>99375</v>
+        <v>99381</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>131731706</v>
       </c>
       <c r="B12" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>131735296</v>
       </c>
       <c r="B13" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1946,10 +1946,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131736743</v>
+        <v>131734447</v>
       </c>
       <c r="B14" t="n">
-        <v>80273</v>
+        <v>99381</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1957,34 +1957,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>219880</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydväst, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558929</v>
+        <v>558943</v>
       </c>
       <c r="R14" t="n">
-        <v>6902582</v>
+        <v>6902405</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131734447</v>
+        <v>131736743</v>
       </c>
       <c r="B15" t="n">
-        <v>99375</v>
+        <v>80275</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2058,34 +2058,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219880</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558943</v>
+        <v>558929</v>
       </c>
       <c r="R15" t="n">
-        <v>6902405</v>
+        <v>6902582</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,32 +2148,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131735294</v>
+        <v>131731709</v>
       </c>
       <c r="B16" t="n">
-        <v>99038</v>
+        <v>79266</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>558938</v>
+        <v>558907</v>
       </c>
       <c r="R16" t="n">
-        <v>6902400</v>
+        <v>6902446</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2249,32 +2249,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131731709</v>
+        <v>131735294</v>
       </c>
       <c r="B17" t="n">
-        <v>79264</v>
+        <v>99044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>558907</v>
+        <v>558938</v>
       </c>
       <c r="R17" t="n">
-        <v>6902446</v>
+        <v>6902400</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,7 +2353,7 @@
         <v>131739130</v>
       </c>
       <c r="B18" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>131737207</v>
       </c>
       <c r="B19" t="n">
-        <v>97909</v>
+        <v>97915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2557,32 +2557,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131733537</v>
+        <v>131731707</v>
       </c>
       <c r="B20" t="n">
-        <v>79520</v>
+        <v>79266</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558903</v>
+        <v>558907</v>
       </c>
       <c r="R20" t="n">
-        <v>6902511</v>
+        <v>6902516</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På torrgran med doftskinn</t>
+          <t>Rikligt på björk i hänsyn</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,32 +2663,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131731707</v>
+        <v>131733537</v>
       </c>
       <c r="B21" t="n">
-        <v>79264</v>
+        <v>79522</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558907</v>
+        <v>558903</v>
       </c>
       <c r="R21" t="n">
-        <v>6902516</v>
+        <v>6902511</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt på björk i hänsyn</t>
+          <t>På torrgran med doftskinn</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2769,10 +2769,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131734449</v>
+        <v>131737206</v>
       </c>
       <c r="B22" t="n">
-        <v>99375</v>
+        <v>97915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,21 +2780,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219880</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2807,7 +2807,7 @@
         <v>558937</v>
       </c>
       <c r="R22" t="n">
-        <v>6902393</v>
+        <v>6902314</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2840,6 +2840,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>I hänsyn med knärot</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2870,10 +2875,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131737206</v>
+        <v>131734449</v>
       </c>
       <c r="B23" t="n">
-        <v>97909</v>
+        <v>99381</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2881,21 +2886,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>219880</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2908,7 +2913,7 @@
         <v>558937</v>
       </c>
       <c r="R23" t="n">
-        <v>6902314</v>
+        <v>6902393</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2941,11 +2946,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>I hänsyn med knärot</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2979,7 +2979,7 @@
         <v>131738278</v>
       </c>
       <c r="B24" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>131731708</v>
       </c>
       <c r="B25" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>131736629</v>
       </c>
       <c r="B26" t="n">
-        <v>80370</v>
+        <v>80372</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>131738281</v>
       </c>
       <c r="B27" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         <v>131738277</v>
       </c>
       <c r="B28" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3491,45 +3491,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131732429</v>
+        <v>131732929</v>
       </c>
       <c r="B29" t="n">
-        <v>98955</v>
+        <v>89223</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219790</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pållesmyran Öst, Mpd</t>
+          <t>Pållesmyran Syd, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558902</v>
+        <v>558900</v>
       </c>
       <c r="R29" t="n">
-        <v>6902247</v>
+        <v>6902511</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3592,10 +3592,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131732929</v>
+        <v>131738279</v>
       </c>
       <c r="B30" t="n">
-        <v>89217</v>
+        <v>80371</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558900</v>
+        <v>558933</v>
       </c>
       <c r="R30" t="n">
-        <v>6902511</v>
+        <v>6902494</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3693,45 +3693,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131738279</v>
+        <v>131732429</v>
       </c>
       <c r="B31" t="n">
-        <v>80369</v>
+        <v>98961</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pållesmyran Syd, Mpd</t>
+          <t>Pållesmyran Öst, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558933</v>
+        <v>558902</v>
       </c>
       <c r="R31" t="n">
-        <v>6902494</v>
+        <v>6902247</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3797,7 +3797,7 @@
         <v>131740501</v>
       </c>
       <c r="B32" t="n">
-        <v>80398</v>
+        <v>80400</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -1946,10 +1946,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131734447</v>
+        <v>131736743</v>
       </c>
       <c r="B14" t="n">
-        <v>99381</v>
+        <v>80275</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1957,34 +1957,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219880</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>558943</v>
+        <v>558929</v>
       </c>
       <c r="R14" t="n">
-        <v>6902405</v>
+        <v>6902582</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2047,10 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131736743</v>
+        <v>131734447</v>
       </c>
       <c r="B15" t="n">
-        <v>80275</v>
+        <v>99381</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2058,34 +2058,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>219880</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydväst, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>558929</v>
+        <v>558943</v>
       </c>
       <c r="R15" t="n">
-        <v>6902582</v>
+        <v>6902405</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2350,32 +2350,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131739130</v>
+        <v>131737207</v>
       </c>
       <c r="B18" t="n">
-        <v>79885</v>
+        <v>97915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558859</v>
+        <v>558887</v>
       </c>
       <c r="R18" t="n">
-        <v>6902252</v>
+        <v>6902256</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2421,11 +2421,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På mycket fin talltorraka</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2456,32 +2451,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131737207</v>
+        <v>131739130</v>
       </c>
       <c r="B19" t="n">
-        <v>97915</v>
+        <v>79885</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2491,10 +2486,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558887</v>
+        <v>558859</v>
       </c>
       <c r="R19" t="n">
-        <v>6902256</v>
+        <v>6902252</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2527,6 +2522,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På mycket fin talltorraka</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -1427,45 +1427,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131740502</v>
+        <v>131735295</v>
       </c>
       <c r="B9" t="n">
-        <v>80400</v>
+        <v>99044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pållesmyran Syd, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558929</v>
+        <v>558934</v>
       </c>
       <c r="R9" t="n">
-        <v>6902492</v>
+        <v>6902394</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1498,6 +1502,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor ligger i hänsyn</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,49 +1537,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131735295</v>
+        <v>131740502</v>
       </c>
       <c r="B10" t="n">
-        <v>99044</v>
+        <v>80400</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Syd, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558934</v>
+        <v>558929</v>
       </c>
       <c r="R10" t="n">
-        <v>6902394</v>
+        <v>6902492</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,11 +1608,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ca 50 plantor ligger i hänsyn</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2350,32 +2350,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131737207</v>
+        <v>131739130</v>
       </c>
       <c r="B18" t="n">
-        <v>97915</v>
+        <v>79885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558887</v>
+        <v>558859</v>
       </c>
       <c r="R18" t="n">
-        <v>6902256</v>
+        <v>6902252</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2421,6 +2421,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På mycket fin talltorraka</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2451,32 +2456,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131739130</v>
+        <v>131737207</v>
       </c>
       <c r="B19" t="n">
-        <v>79885</v>
+        <v>97915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2486,10 +2491,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558859</v>
+        <v>558887</v>
       </c>
       <c r="R19" t="n">
-        <v>6902252</v>
+        <v>6902256</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2522,11 +2527,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På mycket fin talltorraka</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>122747002</v>
       </c>
       <c r="B3" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>122747000</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>122747001</v>
       </c>
       <c r="B5" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>131738280</v>
       </c>
       <c r="B6" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>131738275</v>
       </c>
       <c r="B7" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>131736631</v>
       </c>
       <c r="B8" t="n">
-        <v>80421</v>
+        <v>80423</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1408,45 +1408,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131740502</v>
+        <v>131735295</v>
       </c>
       <c r="B9" t="n">
-        <v>80449</v>
+        <v>99098</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Pållesmyran Syd, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>558929</v>
+        <v>558934</v>
       </c>
       <c r="R9" t="n">
-        <v>6902492</v>
+        <v>6902394</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,6 +1483,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 50 plantor ligger i hänsyn</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,49 +1518,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131735295</v>
+        <v>131740502</v>
       </c>
       <c r="B10" t="n">
-        <v>99095</v>
+        <v>80451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Syd, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>558934</v>
+        <v>558929</v>
       </c>
       <c r="R10" t="n">
-        <v>6902394</v>
+        <v>6902492</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,11 +1589,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ca 50 plantor ligger i hänsyn</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1622,7 +1622,7 @@
         <v>131734446</v>
       </c>
       <c r="B11" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>131731706</v>
       </c>
       <c r="B12" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
         <v>131735296</v>
       </c>
       <c r="B13" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>131736743</v>
       </c>
       <c r="B14" t="n">
-        <v>80324</v>
+        <v>80326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>131734447</v>
       </c>
       <c r="B15" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         <v>131731709</v>
       </c>
       <c r="B16" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>131735294</v>
       </c>
       <c r="B17" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,32 +2331,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131737207</v>
+        <v>131739130</v>
       </c>
       <c r="B18" t="n">
-        <v>97966</v>
+        <v>79936</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>558887</v>
+        <v>558859</v>
       </c>
       <c r="R18" t="n">
-        <v>6902256</v>
+        <v>6902252</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2402,6 +2402,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På mycket fin talltorraka</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2432,32 +2437,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131739130</v>
+        <v>131737207</v>
       </c>
       <c r="B19" t="n">
-        <v>79934</v>
+        <v>97969</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2467,10 +2472,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>558859</v>
+        <v>558887</v>
       </c>
       <c r="R19" t="n">
-        <v>6902252</v>
+        <v>6902256</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2503,11 +2508,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På mycket fin talltorraka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2538,32 +2538,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131733537</v>
+        <v>131731707</v>
       </c>
       <c r="B20" t="n">
-        <v>79571</v>
+        <v>79317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>558903</v>
+        <v>558907</v>
       </c>
       <c r="R20" t="n">
-        <v>6902511</v>
+        <v>6902516</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På torrgran med doftskinn</t>
+          <t>Rikligt på björk i hänsyn</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2644,32 +2644,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131731707</v>
+        <v>131733537</v>
       </c>
       <c r="B21" t="n">
-        <v>79315</v>
+        <v>79573</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2679,10 +2679,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>558907</v>
+        <v>558903</v>
       </c>
       <c r="R21" t="n">
-        <v>6902516</v>
+        <v>6902511</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt på björk i hänsyn</t>
+          <t>På torrgran med doftskinn</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2750,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737206</v>
+        <v>131734449</v>
       </c>
       <c r="B22" t="n">
-        <v>97966</v>
+        <v>99436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2761,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>219880</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2788,7 +2788,7 @@
         <v>558937</v>
       </c>
       <c r="R22" t="n">
-        <v>6902314</v>
+        <v>6902393</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,11 +2821,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>I hänsyn med knärot</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2859,7 +2854,7 @@
         <v>131731708</v>
       </c>
       <c r="B23" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2965,7 +2960,7 @@
         <v>131738278</v>
       </c>
       <c r="B24" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3063,10 +3058,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131734449</v>
+        <v>131737206</v>
       </c>
       <c r="B25" t="n">
-        <v>99433</v>
+        <v>97969</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3074,21 +3069,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219880</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3101,7 +3096,7 @@
         <v>558937</v>
       </c>
       <c r="R25" t="n">
-        <v>6902393</v>
+        <v>6902314</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3134,6 +3129,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I hänsyn med knärot</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3167,7 +3167,7 @@
         <v>131736629</v>
       </c>
       <c r="B26" t="n">
-        <v>80421</v>
+        <v>80423</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>131738281</v>
       </c>
       <c r="B27" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>131738277</v>
       </c>
       <c r="B28" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>131732929</v>
       </c>
       <c r="B29" t="n">
-        <v>89274</v>
+        <v>89277</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>131738279</v>
       </c>
       <c r="B30" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>131732429</v>
       </c>
       <c r="B31" t="n">
-        <v>99012</v>
+        <v>99015</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>131740501</v>
       </c>
       <c r="B32" t="n">
-        <v>80449</v>
+        <v>80451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -2851,10 +2851,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131731708</v>
+        <v>131738278</v>
       </c>
       <c r="B23" t="n">
-        <v>79317</v>
+        <v>80422</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2862,34 +2862,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Pållesmyran Syd, Mpd</t>
+          <t>Pållesmyran Sydväst, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>558898</v>
+        <v>558913</v>
       </c>
       <c r="R23" t="n">
-        <v>6902495</v>
+        <v>6902578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2922,11 +2922,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-26</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gamla granar mot våtmark</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2957,45 +2952,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131738278</v>
+        <v>131737206</v>
       </c>
       <c r="B24" t="n">
-        <v>80422</v>
+        <v>97969</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydväst, Mpd</t>
+          <t>Pållesmyran Sydost, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>558913</v>
+        <v>558937</v>
       </c>
       <c r="R24" t="n">
-        <v>6902578</v>
+        <v>6902314</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3028,6 +3023,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>I hänsyn med knärot</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3058,45 +3058,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131737206</v>
+        <v>131731708</v>
       </c>
       <c r="B25" t="n">
-        <v>97969</v>
+        <v>79317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Pållesmyran Sydost, Mpd</t>
+          <t>Pållesmyran Syd, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>558937</v>
+        <v>558898</v>
       </c>
       <c r="R25" t="n">
-        <v>6902314</v>
+        <v>6902495</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>I hänsyn med knärot</t>
+          <t>På gamla granar mot våtmark</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -3472,45 +3472,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131732929</v>
+        <v>131732429</v>
       </c>
       <c r="B29" t="n">
-        <v>89277</v>
+        <v>99015</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>219790</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Pållesmyran Syd, Mpd</t>
+          <t>Pållesmyran Öst, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>558900</v>
+        <v>558902</v>
       </c>
       <c r="R29" t="n">
-        <v>6902511</v>
+        <v>6902247</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3573,10 +3573,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131738279</v>
+        <v>131732929</v>
       </c>
       <c r="B30" t="n">
-        <v>80422</v>
+        <v>89277</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3584,21 +3584,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>558933</v>
+        <v>558900</v>
       </c>
       <c r="R30" t="n">
-        <v>6902494</v>
+        <v>6902511</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3674,45 +3674,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131732429</v>
+        <v>131738279</v>
       </c>
       <c r="B31" t="n">
-        <v>99015</v>
+        <v>80422</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Pållesmyran Öst, Mpd</t>
+          <t>Pållesmyran Syd, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>558902</v>
+        <v>558933</v>
       </c>
       <c r="R31" t="n">
-        <v>6902247</v>
+        <v>6902494</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>122747002</v>
       </c>
       <c r="B3" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>122747000</v>
       </c>
       <c r="B4" t="n">
-        <v>91912</v>
+        <v>91918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>122747001</v>
       </c>
       <c r="B5" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>122747002</v>
       </c>
       <c r="B3" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>122747000</v>
       </c>
       <c r="B4" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>122747001</v>
       </c>
       <c r="B5" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>122747000</v>
       </c>
       <c r="B4" t="n">
-        <v>91928</v>
+        <v>91929</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47617-2024 artfynd.xlsx
+++ b/artfynd/A 47617-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732929</t>
         </is>
       </c>
     </row>
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88309178</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736629</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736631</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734474</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131731705</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1384,6 +1419,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131731706</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131731707</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131731708</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,6 +1747,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131731709</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733412</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1904,6 +1964,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739130</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2005,6 +2070,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736743</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2111,6 +2181,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747001</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2217,6 +2292,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122747002</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2323,6 +2403,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738269</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2424,6 +2509,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738275</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2525,6 +2615,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738277</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2626,6 +2721,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738278</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2727,6 +2827,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738279</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2828,6 +2933,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738280</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2934,6 +3044,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738281</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3040,6 +3155,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733537</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3141,6 +3261,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740501</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3242,6 +3367,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740502</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3343,6 +3473,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131733267</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3444,6 +3579,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732427</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3545,6 +3685,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732429</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3646,6 +3791,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734446</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3747,6 +3897,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734447</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3848,6 +4003,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734449</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3949,6 +4109,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734346</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4050,6 +4215,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734347</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4151,6 +4321,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732448</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4252,6 +4427,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732450</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4353,6 +4533,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735294</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4463,6 +4648,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735295</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4564,6 +4754,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735296</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4670,6 +4865,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737206</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4771,6 +4971,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737207</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4872,6 +5077,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737241</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4978,8 +5188,57 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734611</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>